--- a/artfynd/A 59396-2022 artfynd.xlsx
+++ b/artfynd/A 59396-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59396-2022 artfynd.xlsx
+++ b/artfynd/A 59396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111486562</v>
+        <v>111486563</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610236.2225055038</v>
+        <v>610238</v>
       </c>
       <c r="R2" t="n">
-        <v>6897513.563481026</v>
+        <v>6897509</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111486573</v>
+        <v>111486576</v>
       </c>
       <c r="B3" t="n">
-        <v>96383</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223621</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610146.8202491006</v>
+        <v>610214</v>
       </c>
       <c r="R3" t="n">
-        <v>6897400.387088978</v>
+        <v>6897284</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111486570</v>
+        <v>111486560</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610138.2204190179</v>
+        <v>610243</v>
       </c>
       <c r="R4" t="n">
-        <v>6897377.214110524</v>
+        <v>6897536</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111486565</v>
+        <v>111486583</v>
       </c>
       <c r="B5" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610237.2946205279</v>
+        <v>610170</v>
       </c>
       <c r="R5" t="n">
-        <v>6897509.394074276</v>
+        <v>6897390</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111486559</v>
+        <v>111486582</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610236.04261225</v>
+        <v>610142</v>
       </c>
       <c r="R6" t="n">
-        <v>6897547.660441305</v>
+        <v>6897317</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,19 +1131,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1163,7 @@
         <v>111486567</v>
       </c>
       <c r="B7" t="n">
-        <v>93057</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610195.0273142112</v>
+        <v>610196</v>
       </c>
       <c r="R7" t="n">
-        <v>6897457.090065848</v>
+        <v>6897457</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1228,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111486560</v>
+        <v>111486568</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610242.9519009186</v>
+        <v>610178</v>
       </c>
       <c r="R8" t="n">
-        <v>6897536.674650873</v>
+        <v>6897404</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,19 +1325,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111486574</v>
+        <v>111486551</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610224.6307519674</v>
+        <v>610207</v>
       </c>
       <c r="R9" t="n">
-        <v>6897324.444504307</v>
+        <v>6897622</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,19 +1422,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111486566</v>
+        <v>111486569</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610196.0688674429</v>
+        <v>610141</v>
       </c>
       <c r="R10" t="n">
-        <v>6897453.853924472</v>
+        <v>6897392</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,33 +1519,17 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på mossbeväxt block</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111486547</v>
+        <v>111486548</v>
       </c>
       <c r="B11" t="n">
-        <v>76495</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610214.3838179935</v>
+        <v>610211</v>
       </c>
       <c r="R11" t="n">
-        <v>6897609.083555548</v>
+        <v>6897612</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,19 +1616,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111486563</v>
+        <v>111486585</v>
       </c>
       <c r="B12" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610237.2946205279</v>
+        <v>610348</v>
       </c>
       <c r="R12" t="n">
-        <v>6897509.394074276</v>
+        <v>6897598</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,19 +1713,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111486571</v>
+        <v>111486578</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610186.5997174035</v>
+        <v>610248</v>
       </c>
       <c r="R13" t="n">
-        <v>6897342.822581144</v>
+        <v>6897273</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,19 +1810,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111486585</v>
+        <v>111486554</v>
       </c>
       <c r="B14" t="n">
-        <v>73634</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610347.1442693399</v>
+        <v>610207</v>
       </c>
       <c r="R14" t="n">
-        <v>6897598.013066654</v>
+        <v>6897581</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,19 +1907,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111486583</v>
+        <v>111486556</v>
       </c>
       <c r="B15" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>610170.0873515971</v>
+        <v>610194</v>
       </c>
       <c r="R15" t="n">
-        <v>6897389.935445569</v>
+        <v>6897572</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2210,19 +2004,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111486556</v>
+        <v>111486584</v>
       </c>
       <c r="B16" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610193.6094834032</v>
+        <v>610335</v>
       </c>
       <c r="R16" t="n">
-        <v>6897571.966054032</v>
+        <v>6897578</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2322,19 +2101,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111486572</v>
+        <v>111486547</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610186.866762756</v>
+        <v>610214</v>
       </c>
       <c r="R17" t="n">
-        <v>6897391.885662847</v>
+        <v>6897609</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2434,19 +2198,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,12 +2230,7 @@
         <v>111486564</v>
       </c>
       <c r="B18" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>610237.2946205279</v>
+        <v>610238</v>
       </c>
       <c r="R18" t="n">
-        <v>6897509.394074276</v>
+        <v>6897509</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2546,19 +2295,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,12 +2327,7 @@
         <v>111486557</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2625,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610221.9365824561</v>
+        <v>610222</v>
       </c>
       <c r="R19" t="n">
-        <v>6897535.519929474</v>
+        <v>6897536</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2658,19 +2392,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111486576</v>
+        <v>111486559</v>
       </c>
       <c r="B20" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>610214.2438761768</v>
+        <v>610236</v>
       </c>
       <c r="R20" t="n">
-        <v>6897284.393316317</v>
+        <v>6897547</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2770,19 +2489,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111486552</v>
+        <v>111486562</v>
       </c>
       <c r="B21" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>610202.9845822605</v>
+        <v>610236</v>
       </c>
       <c r="R21" t="n">
-        <v>6897614.31648521</v>
+        <v>6897514</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2882,19 +2586,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111486577</v>
+        <v>111486566</v>
       </c>
       <c r="B22" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2961,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>610245.4727674432</v>
+        <v>610197</v>
       </c>
       <c r="R22" t="n">
-        <v>6897273.734988614</v>
+        <v>6897454</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2994,19 +2683,14 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på mossbeväxt block</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,6 +2699,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3033,37 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111486584</v>
+        <v>111486570</v>
       </c>
       <c r="B23" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3073,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>610335.6047682473</v>
+        <v>610138</v>
       </c>
       <c r="R23" t="n">
-        <v>6897578.948932082</v>
+        <v>6897378</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3106,19 +2786,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,37 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111486569</v>
+        <v>111486571</v>
       </c>
       <c r="B24" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>610141.0038371853</v>
+        <v>610187</v>
       </c>
       <c r="R24" t="n">
-        <v>6897392.254898546</v>
+        <v>6897343</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,19 +2883,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,37 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111486554</v>
+        <v>111486572</v>
       </c>
       <c r="B25" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>610206.4050188576</v>
+        <v>610187</v>
       </c>
       <c r="R25" t="n">
-        <v>6897581.260525526</v>
+        <v>6897392</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3330,19 +2980,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,37 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111486568</v>
+        <v>111486574</v>
       </c>
       <c r="B26" t="n">
-        <v>93057</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>610178.0574054071</v>
+        <v>610225</v>
       </c>
       <c r="R26" t="n">
-        <v>6897403.74427297</v>
+        <v>6897324</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3442,19 +3077,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,15 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111486586</v>
+        <v>111486575</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3521,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>610319.2657305499</v>
+        <v>610234</v>
       </c>
       <c r="R27" t="n">
-        <v>6897606.443173738</v>
+        <v>6897285</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3554,19 +3174,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,37 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111486578</v>
+        <v>111486580</v>
       </c>
       <c r="B28" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3633,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610248.2770640558</v>
+        <v>610100</v>
       </c>
       <c r="R28" t="n">
-        <v>6897273.826739896</v>
+        <v>6897187</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3666,19 +3271,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3705,15 +3300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111486575</v>
+        <v>111486581</v>
       </c>
       <c r="B29" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610234.356536509</v>
+        <v>610072</v>
       </c>
       <c r="R29" t="n">
-        <v>6897284.584036393</v>
+        <v>6897129</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3778,19 +3368,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3817,37 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111486551</v>
+        <v>111486586</v>
       </c>
       <c r="B30" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3857,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>610206.9311065455</v>
+        <v>610320</v>
       </c>
       <c r="R30" t="n">
-        <v>6897622.387123355</v>
+        <v>6897607</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3890,19 +3465,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3929,37 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111486581</v>
+        <v>111486573</v>
       </c>
       <c r="B31" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99155</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>223621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3969,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>610072.3796948178</v>
+        <v>610147</v>
       </c>
       <c r="R31" t="n">
-        <v>6897129.783162965</v>
+        <v>6897400</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4002,19 +3562,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4041,15 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111486548</v>
+        <v>111486577</v>
       </c>
       <c r="B32" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4057,21 +3602,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4081,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>610211.0056098022</v>
+        <v>610245</v>
       </c>
       <c r="R32" t="n">
-        <v>6897612.243104065</v>
+        <v>6897274</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4114,19 +3659,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4153,15 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111486582</v>
+        <v>111486579</v>
       </c>
       <c r="B33" t="n">
-        <v>88489</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4193,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>610142.0730319817</v>
+        <v>610298</v>
       </c>
       <c r="R33" t="n">
-        <v>6897316.605782338</v>
+        <v>6897156</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4226,27 +3756,18 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4265,37 +3786,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111486580</v>
+        <v>111486552</v>
       </c>
       <c r="B34" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4305,10 +3821,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>610100.4635512675</v>
+        <v>610203</v>
       </c>
       <c r="R34" t="n">
-        <v>6897186.766084836</v>
+        <v>6897614</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4338,19 +3854,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,6 +3880,103 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>111486565</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grimåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>610238</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6897509</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59396-2022 artfynd.xlsx
+++ b/artfynd/A 59396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486560</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486582</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486567</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486568</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486551</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486548</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486585</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486578</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486554</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486556</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486547</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486564</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486557</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486559</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486562</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2715,6 +2820,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486566</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2812,6 +2922,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486570</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2909,6 +3024,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486571</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3006,6 +3126,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486572</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3103,6 +3228,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486574</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3200,6 +3330,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486575</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3297,6 +3432,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486580</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3394,6 +3534,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486581</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3491,6 +3636,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486586</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3588,6 +3738,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486573</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3685,6 +3840,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486577</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3783,6 +3943,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486579</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3880,6 +4045,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486552</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3977,8 +4147,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111486565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>